--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.11758132979503</v>
+        <v>10.41910696609169</v>
       </c>
       <c r="D2" t="n">
-        <v>65.06526943476852</v>
+        <v>10.57310628314988</v>
       </c>
       <c r="E2" t="n">
-        <v>21.96488593580224</v>
+        <v>3.569293964567864</v>
       </c>
       <c r="F2" t="n">
-        <v>22.22998175513941</v>
+        <v>3.612372035210153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.18780945819056</v>
+        <v>3.280519036955966</v>
       </c>
       <c r="D3" t="n">
-        <v>20.60530592448972</v>
+        <v>3.348362212729579</v>
       </c>
       <c r="E3" t="n">
-        <v>21.96488593580224</v>
+        <v>3.569293964567864</v>
       </c>
       <c r="F3" t="n">
-        <v>22.22998175513941</v>
+        <v>3.612372035210153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
